--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.14.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.14.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0014.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0014.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L14: isolated marker/symbol line :: 1</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: /</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,10 +670,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 26</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: a</t>
+          <t>L3: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -714,11 +726,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the Parliament of Upper Canada,â€”7th Wm. 4, ch. 2,</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -728,7 +736,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: -</t>
+          <t>L5: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -750,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -765,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cery in England" in respect of the following matters :â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -777,7 +781,11 @@
           <t>L36: symbol-only separator/garbage line :: 1837.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -820,7 +828,11 @@
           <t>L41: isolated marker/symbol line :: "</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L62: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -903,7 +915,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -944,7 +956,11 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
@@ -965,12 +981,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1009,7 +1025,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1043,12 +1059,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1126,7 +1142,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
